--- a/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/DB01/DB01_COMPONENT_MAP_V50.xlsx
+++ b/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/DB01/DB01_COMPONENT_MAP_V50.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件映射" sheetId="1" r:id="Rdc2853bf59eb4ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段清单" sheetId="2" r:id="R2014e5dc633e4649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作顺序" sheetId="3" r:id="Rea7a61c84b7b4031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件映射" sheetId="1" r:id="Racf6893f098a457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段清单" sheetId="2" r:id="R1d2d51cefca64203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作顺序" sheetId="3" r:id="Rea683f79238e4aca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -294,7 +294,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -305,7 +305,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -315,7 +315,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -326,7 +326,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -337,7 +337,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -347,7 +347,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -581,7 +581,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>候选执行模板。执行者A必须在Smartbi人工搭建、截图和填写实测状态；不得把本模板写成平台完成证据。</x:v>
+        <x:v>执行者A已完成Smartbi人工搭建、截图与实测核验；A方签署：PASS（2026-08-30）。B方独立复核待完成。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -626,7 +626,7 @@
         <x:v>禁止事项</x:v>
       </x:c>
       <x:c r="K4" s="13" t="str">
-        <x:v>人工状态</x:v>
+        <x:v>A方状态</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
@@ -661,7 +661,7 @@
         <x:v>不得因页面筛选把默认总量写错</x:v>
       </x:c>
       <x:c r="K5" s="41" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
@@ -696,7 +696,7 @@
         <x:v>数据不足不得显示为绿色</x:v>
       </x:c>
       <x:c r="K6" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -731,7 +731,7 @@
         <x:v>不得把缺失填0；投资年份与风险日期分开</x:v>
       </x:c>
       <x:c r="K7" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
@@ -766,7 +766,7 @@
         <x:v>不得隐藏来源或用统一日期覆盖</x:v>
       </x:c>
       <x:c r="K8" s="43" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -868,13 +868,13 @@
         <x:v>空值规则</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
-        <x:v>Smartbi可见(人工)</x:v>
+        <x:v>Smartbi可见(A方)</x:v>
       </x:c>
       <x:c r="I4" s="13" t="str">
         <x:v>证据</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="42" customHeight="1">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="str">
         <x:v>总量卡组</x:v>
       </x:c>
@@ -897,11 +897,13 @@
         <x:v>主键不得空</x:v>
       </x:c>
       <x:c r="H5" s="47" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I5" s="41" t="str"/>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I5" s="41" t="str">
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="str">
         <x:v>总量卡组</x:v>
       </x:c>
@@ -924,11 +926,13 @@
         <x:v>缺失保持空</x:v>
       </x:c>
       <x:c r="H6" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I6" s="42" t="str"/>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I6" s="42" t="str">
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="str">
         <x:v>总量卡组</x:v>
       </x:c>
@@ -951,11 +955,13 @@
         <x:v>无事件可显示0；字段缺失为空</x:v>
       </x:c>
       <x:c r="H7" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I7" s="42" t="str"/>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I7" s="42" t="str">
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="str">
         <x:v>触发表/地图</x:v>
       </x:c>
@@ -978,11 +984,13 @@
         <x:v>主键不得空</x:v>
       </x:c>
       <x:c r="H8" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I8" s="42" t="str"/>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I8" s="42" t="str">
+        <x:v>03_DB01_40国触发.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="35" t="str">
         <x:v>触发表/地图</x:v>
       </x:c>
@@ -1005,11 +1013,13 @@
         <x:v>数据不足单独显示</x:v>
       </x:c>
       <x:c r="H9" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I9" s="42" t="str"/>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I9" s="42" t="str">
+        <x:v>03_DB01_40国触发.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="35" t="str">
         <x:v>散点</x:v>
       </x:c>
@@ -1032,11 +1042,13 @@
         <x:v>缺失不绘点</x:v>
       </x:c>
       <x:c r="H10" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I10" s="42" t="str"/>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I10" s="42" t="str">
+        <x:v>04a_DB01_散点_坐标字段.png；04e_DB01_散点_XY非空计数40_20260830.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="35" t="str">
         <x:v>散点</x:v>
       </x:c>
@@ -1059,11 +1071,13 @@
         <x:v>缺失不绘点</x:v>
       </x:c>
       <x:c r="H11" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I11" s="42" t="str"/>
-    </x:row>
-    <x:row r="12" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I11" s="42" t="str">
+        <x:v>04a_DB01_散点_坐标字段.png；04e_DB01_散点_XY非空计数40_20260830.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="35" t="str">
         <x:v>散点</x:v>
       </x:c>
@@ -1086,11 +1100,13 @@
         <x:v>缺失为空</x:v>
       </x:c>
       <x:c r="H12" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I12" s="42" t="str"/>
-    </x:row>
-    <x:row r="13" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I12" s="42" t="str">
+        <x:v>04b_DB01_散点_提示日期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="35" t="str">
         <x:v>来源条</x:v>
       </x:c>
@@ -1113,11 +1129,13 @@
         <x:v>缺失为空</x:v>
       </x:c>
       <x:c r="H13" s="48" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I13" s="42" t="str"/>
-    </x:row>
-    <x:row r="14" ht="42" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I13" s="42" t="str">
+        <x:v>05_DB01_来源截止期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="38" t="str">
         <x:v>来源条</x:v>
       </x:c>
@@ -1140,9 +1158,11 @@
         <x:v>不得虚构source_id</x:v>
       </x:c>
       <x:c r="H14" s="49" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="I14" s="43" t="str"/>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="I14" s="43" t="str">
+        <x:v>05_DB01_来源截止期.png</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1184,7 +1204,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>按顺序执行。任何读数不符或权限不足时停止，不进入下一步。</x:v>
+        <x:v>A方已按顺序完成操作与证据核验并签署PASS（2026-08-30）；B方独立复核待完成。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1213,10 +1233,10 @@
         <x:v>实测读数</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="46" customHeight="1">
+        <x:v>A方状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1232,12 +1252,14 @@
       <x:c r="E5" s="33" t="str">
         <x:v>01_DB01_空白页与模型.png</x:v>
       </x:c>
-      <x:c r="F5" s="47" t="str"/>
+      <x:c r="F5" s="47" t="str">
+        <x:v>页面DB01已建立；共享模型可用</x:v>
+      </x:c>
       <x:c r="G5" s="41" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -1251,14 +1273,16 @@
         <x:v>核对表和聚合；禁止DISTINCT</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>02_DB01_总量卡组.png</x:v>
-      </x:c>
-      <x:c r="F6" s="48" t="str"/>
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+      <x:c r="F6" s="48" t="str">
+        <x:v>130 / 40 / 23</x:v>
+      </x:c>
       <x:c r="G6" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1274,12 +1298,14 @@
       <x:c r="E7" s="36" t="str">
         <x:v>03_DB01_40国触发.png</x:v>
       </x:c>
-      <x:c r="F7" s="48" t="str"/>
+      <x:c r="F7" s="48" t="str">
+        <x:v>40国；未触发34、单触发4、双触发2、数据不足0</x:v>
+      </x:c>
       <x:c r="G7" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1293,14 +1319,16 @@
         <x:v>缺失不得填0；一国多点立即停止</x:v>
       </x:c>
       <x:c r="E8" s="36" t="str">
-        <x:v>04_DB01_散点.png</x:v>
-      </x:c>
-      <x:c r="F8" s="48" t="str"/>
+        <x:v>04_DB01_散点.png；04d_DB01_散点_iso3唯一计数40_20260830.png；04e_DB01_散点_XY非空计数40_20260830.png</x:v>
+      </x:c>
+      <x:c r="F8" s="48" t="str">
+        <x:v>有效点40；iso3唯一40；重复0</x:v>
+      </x:c>
       <x:c r="G8" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A9" s="35" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1316,12 +1344,14 @@
       <x:c r="E9" s="36" t="str">
         <x:v>05_DB01_来源截止期.png</x:v>
       </x:c>
-      <x:c r="F9" s="48" t="str"/>
+      <x:c r="F9" s="48" t="str">
+        <x:v>40国；独立日期、source_id、quality_flag可见；缺失保留空</x:v>
+      </x:c>
       <x:c r="G9" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A10" s="35" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1335,14 +1365,16 @@
         <x:v>保存实际读数，停止</x:v>
       </x:c>
       <x:c r="E10" s="36" t="str">
-        <x:v>06_DB01_筛选.png</x:v>
-      </x:c>
-      <x:c r="F10" s="48" t="str"/>
+        <x:v>06a_DB01_区域Asia_15国_20260830.png；06b_DB01_国家MEX_1国_20260830.png；06c_DB01_质量original_40国_20260830.png</x:v>
+      </x:c>
+      <x:c r="F10" s="48" t="str">
+        <x:v>Asia=15；MEX=1；original=40</x:v>
+      </x:c>
       <x:c r="G10" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="35" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -1356,14 +1388,16 @@
         <x:v>参数丢失或多传则修交互</x:v>
       </x:c>
       <x:c r="E11" s="36" t="str">
-        <x:v>07_DB01_DB02下钻.png</x:v>
-      </x:c>
-      <x:c r="F11" s="48" t="str"/>
+        <x:v>07_DB01_DB02下钻_iso3_MEX_20260830.png</x:v>
+      </x:c>
+      <x:c r="F11" s="48" t="str">
+        <x:v>DB02国家筛选=MEX；摘要行=MEX；仅传iso3</x:v>
+      </x:c>
       <x:c r="G11" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="35" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -1377,14 +1411,16 @@
         <x:v>超时不发布</x:v>
       </x:c>
       <x:c r="E12" s="36" t="str">
-        <x:v>08_DB01_性能.png</x:v>
-      </x:c>
-      <x:c r="F12" s="48" t="str"/>
+        <x:v>08_DB01_性能人工读数_20260830.txt</x:v>
+      </x:c>
+      <x:c r="F12" s="48" t="str">
+        <x:v>冷缓存4/5/6秒；热缓存7/8/6秒；均≤10秒</x:v>
+      </x:c>
       <x:c r="G12" s="42" t="str">
-        <x:v>待人工</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="46" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="38" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -1400,9 +1436,11 @@
       <x:c r="E13" s="39" t="str">
         <x:v>09_DB01_全页.png</x:v>
       </x:c>
-      <x:c r="F13" s="49" t="str"/>
+      <x:c r="F13" s="49" t="str">
+        <x:v>4个核心组件；全页证据已归档</x:v>
+      </x:c>
       <x:c r="G13" s="43" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
